--- a/docs/requirement_analysis/要件定義_TEM_DM3.xlsx
+++ b/docs/requirement_analysis/要件定義_TEM_DM3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-22.04\home\rde2\gitlab\RDE_ELECTRON_MICROSCOPE_STANDARD\docs\requirement_analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\a022223\work\RDE\em_standard_dataset_template_nomethod\em_standard_dataset_template\docs\requirement_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD1E18BB-621E-4822-97B6-62E2CAEE97BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D6F2EE4-0FD2-4E1D-BFE3-BFB9B67BC637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="851" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="851" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="要件定義（手入力 メタデータ項目リスト）_bak" sheetId="15" state="hidden" r:id="rId1"/>
@@ -88,6 +88,17 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -101,38 +112,20 @@
   <commentList>
     <comment ref="F26" authorId="0" shapeId="0" xr:uid="{8EC9289B-E89B-C54A-AF5E-A9CAB7783195}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Yu Gothic"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[スレッド化されたコメント]
+        <t>[スレッド化されたコメント]
 使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
 コメント:
     「スパイク除去/spike removal」などとするのが良いでしょう。（特異点除去という言葉は物理学上かなり特定の意味を持つ言葉で、今回の処理はそれに当たらないため）
 返信:
 OKです。</t>
-        </r>
       </text>
     </comment>
     <comment ref="F27" authorId="1" shapeId="0" xr:uid="{296B8175-6133-1340-B050-FB33F3C0CC15}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Yu Gothic"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[スレッド化されたコメント]
+        <t>[スレッド化されたコメント]
 使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
 コメント:
     「取得」というか、「特出し表示」？　取得でも良いですが、一応議論したく</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -150,15 +143,7 @@
   <commentList>
     <comment ref="L27" authorId="0" shapeId="0" xr:uid="{AD545E9C-6EAD-7444-868D-1DA9DDED3D54}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Yu Gothic"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[スレッド化されたコメント]
+        <t>[スレッド化されたコメント]
 使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
 コメント:
     数値型に固執させるなら、サンプル幅・サンプル長さ・サンプル厚さの3項目に分ける必要が出てきますか？
@@ -166,56 +151,29 @@
 はい、そう思います。DX的にそうするのか、現場の実情に合わせてこのようにするのか、コメント欄（SAMPLE_COMMENT）に特別なルールを設けてSAMPLE_SIZEやSAMPLE_VOLUMEに計算してマッピングするか、などが考えられると思います。
 送り状にこの3つの項目を持たせようと思っていますが、それとの関係も検討必要です。
 DXにこだわりすぎて、実情に合わないことをやっても仕方ないと思いますので悩みます。</t>
-        </r>
       </text>
     </comment>
     <comment ref="F36" authorId="1" shapeId="0" xr:uid="{14C21C5E-7A44-AA48-B84A-2B7A0F5A94D8}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Yu Gothic"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[スレッド化されたコメント]
+        <t>[スレッド化されたコメント]
 使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
 コメント:
     "coercivity" のようなちゃんとした英語名ではなく、記号を英語名扱いで格納するということでいいなら、これでOKです。この下のセルも同様
 返信:
 確かにそうですね。基本的に略語は使用しない、という原則で考えていますが、磁性分野では常識な語彙なのでOKと考えるか、ということですね。</t>
-        </r>
       </text>
     </comment>
     <comment ref="H37" authorId="2" shapeId="0" xr:uid="{C11FE378-AC52-5844-93E3-10FA1B4B2ECC}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Yu Gothic"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[スレッド化されたコメント]
+        <t>[スレッド化されたコメント]
 使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
 コメント:
     emuは標準単位系ではないので、高橋さん用途には良いとしても、汎用としては別の単位に換算すべきな気がする</t>
-        </r>
       </text>
     </comment>
     <comment ref="F39" authorId="3" shapeId="0" xr:uid="{EFCB1198-F542-704F-9335-CDD4A0F5BC07}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Yu Gothic"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>[スレッド化されたコメント]
+        <t>[スレッド化されたコメント]
 使用している Excel のバージョンでは、このスレッド化されたコメントを表示できますが、新しいバージョンの Excel でファイルを開いた場合はコメントに対する編集がすべて削除されます。詳細: https://go.microsoft.com/fwlink/?linkid=870924
 コメント:
     Br per volume か？
@@ -235,7 +193,6 @@
 高橋さんのメタは
 「残留磁化x膜厚(memu):3.92e-03」
 となっており、残留磁化はBrを使用しています。整理必要かもしれません。</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -243,21 +200,21 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
   <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
-        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="0"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
-        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="1"/>
         </ext>
       </extLst>
@@ -1535,6 +1492,13 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
+    <t>笹島</t>
+    <rPh sb="0" eb="2">
+      <t>ササジマ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
     <t>非共有rawデータファイル</t>
     <rPh sb="0" eb="1">
       <t>ヒ</t>
@@ -3520,10 +3484,6 @@
     <rPh sb="10" eb="12">
       <t>コテイ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>NIMS</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -8565,7 +8525,7 @@
         <v>45685</v>
       </c>
       <c r="C5" s="69" t="s">
-        <v>830</v>
+        <v>278</v>
       </c>
       <c r="D5" s="69"/>
       <c r="E5" s="70" t="s">
@@ -10045,32 +10005,32 @@
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -10117,16 +10077,16 @@
         <v>6</v>
       </c>
       <c r="K1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O1" s="102" t="s">
         <v>7</v>
@@ -10134,7 +10094,7 @@
     </row>
     <row r="2" spans="1:15" ht="150.75" thickBot="1">
       <c r="C2" s="103" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D2" s="104" t="s">
         <v>9</v>
@@ -10158,16 +10118,16 @@
         <v>15</v>
       </c>
       <c r="K2" s="107" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L2" s="107" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M2" s="107" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N2" s="107" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O2" s="108" t="s">
         <v>16</v>
@@ -10194,7 +10154,7 @@
       <c r="I3" s="19"/>
       <c r="J3" s="19"/>
       <c r="K3" s="20" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="L3" s="24"/>
       <c r="M3" s="113"/>
@@ -10511,10 +10471,10 @@
       <c r="D15" s="31"/>
       <c r="E15" s="31"/>
       <c r="F15" s="32" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="G15" s="23" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="H15" s="32" t="s">
         <v>27</v>
@@ -10717,15 +10677,15 @@
         <v>272</v>
       </c>
       <c r="C23" s="109" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D23" s="110"/>
       <c r="E23" s="179"/>
       <c r="F23" s="109" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G23" s="109" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H23" s="111" t="s">
         <v>21</v>
@@ -10737,22 +10697,22 @@
       <c r="M23" s="113"/>
       <c r="N23" s="113"/>
       <c r="O23" s="180" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="214"/>
       <c r="B24" s="200"/>
       <c r="C24" s="109" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D24" s="110"/>
       <c r="E24" s="179"/>
       <c r="F24" s="109" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G24" s="109" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H24" s="111" t="s">
         <v>21</v>
@@ -10764,22 +10724,22 @@
       <c r="M24" s="113"/>
       <c r="N24" s="113"/>
       <c r="O24" s="180" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="214"/>
       <c r="B25" s="200"/>
       <c r="C25" s="109" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D25" s="110"/>
       <c r="E25" s="179"/>
       <c r="F25" s="109" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G25" s="109" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H25" s="111" t="s">
         <v>200</v>
@@ -10798,15 +10758,15 @@
       <c r="A26" s="214"/>
       <c r="B26" s="200"/>
       <c r="C26" s="114" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D26" s="115"/>
       <c r="E26" s="115"/>
       <c r="F26" s="116" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G26" s="116" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H26" s="117" t="s">
         <v>200</v>
@@ -10818,22 +10778,22 @@
       <c r="M26" s="119"/>
       <c r="N26" s="119"/>
       <c r="O26" s="120" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="214"/>
       <c r="B27" s="200"/>
       <c r="C27" s="109" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D27" s="110"/>
       <c r="E27" s="22"/>
       <c r="F27" s="109" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G27" s="109" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H27" s="111" t="s">
         <v>21</v>
@@ -10842,7 +10802,7 @@
       <c r="J27" s="112"/>
       <c r="K27" s="112"/>
       <c r="L27" s="112" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M27" s="113"/>
       <c r="N27" s="113"/>
@@ -10852,21 +10812,21 @@
       <c r="A28" s="214"/>
       <c r="B28" s="200"/>
       <c r="C28" s="109" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D28" s="110"/>
       <c r="E28" s="110"/>
       <c r="F28" s="109" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G28" s="109" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H28" s="122" t="s">
         <v>200</v>
       </c>
       <c r="I28" s="112" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J28" s="112"/>
       <c r="K28" s="112"/>
@@ -10879,21 +10839,21 @@
       <c r="A29" s="214"/>
       <c r="B29" s="200"/>
       <c r="C29" s="109" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D29" s="110"/>
       <c r="E29" s="110"/>
       <c r="F29" s="109" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G29" s="109" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H29" s="122" t="s">
         <v>200</v>
       </c>
       <c r="I29" s="112" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J29" s="112"/>
       <c r="K29" s="112"/>
@@ -10906,21 +10866,21 @@
       <c r="A30" s="214"/>
       <c r="B30" s="200"/>
       <c r="C30" s="109" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D30" s="110"/>
       <c r="E30" s="110"/>
       <c r="F30" s="109" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G30" s="109" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H30" s="122" t="s">
         <v>200</v>
       </c>
       <c r="I30" s="112" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J30" s="112"/>
       <c r="K30" s="112"/>
@@ -10933,15 +10893,15 @@
       <c r="A31" s="214"/>
       <c r="B31" s="200"/>
       <c r="C31" s="109" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D31" s="110"/>
       <c r="E31" s="110"/>
       <c r="F31" s="109" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G31" s="109" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H31" s="122" t="s">
         <v>21</v>
@@ -10958,21 +10918,21 @@
       <c r="A32" s="214"/>
       <c r="B32" s="200"/>
       <c r="C32" s="109" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D32" s="110"/>
       <c r="E32" s="110"/>
       <c r="F32" s="109" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G32" s="109" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H32" s="122" t="s">
         <v>21</v>
       </c>
       <c r="I32" s="112" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J32" s="112"/>
       <c r="K32" s="112"/>
@@ -10985,15 +10945,15 @@
       <c r="A33" s="214"/>
       <c r="B33" s="200"/>
       <c r="C33" s="114" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D33" s="115"/>
       <c r="E33" s="115"/>
       <c r="F33" s="116" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G33" s="116" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H33" s="117" t="s">
         <v>200</v>
@@ -11010,15 +10970,15 @@
       <c r="A34" s="214"/>
       <c r="B34" s="200"/>
       <c r="C34" s="123" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D34" s="124"/>
       <c r="E34" s="124"/>
       <c r="F34" s="125" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G34" s="125" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H34" s="126" t="s">
         <v>21</v>
@@ -11027,7 +10987,7 @@
       <c r="J34" s="127"/>
       <c r="K34" s="127"/>
       <c r="L34" s="127" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M34" s="128"/>
       <c r="N34" s="128"/>
@@ -11037,21 +10997,21 @@
       <c r="A35" s="214"/>
       <c r="B35" s="200"/>
       <c r="C35" s="109" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D35" s="110"/>
       <c r="E35" s="110"/>
       <c r="F35" s="109" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G35" s="109" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H35" s="122" t="s">
         <v>200</v>
       </c>
       <c r="I35" s="112" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J35" s="112"/>
       <c r="K35" s="112"/>
@@ -11064,21 +11024,21 @@
       <c r="A36" s="214"/>
       <c r="B36" s="200"/>
       <c r="C36" s="109" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D36" s="110"/>
       <c r="E36" s="110"/>
       <c r="F36" s="109" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G36" s="109" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H36" s="122" t="s">
         <v>200</v>
       </c>
       <c r="I36" s="112" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J36" s="112"/>
       <c r="K36" s="112"/>
@@ -11091,15 +11051,15 @@
       <c r="A37" s="214"/>
       <c r="B37" s="200"/>
       <c r="C37" s="109" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D37" s="110"/>
       <c r="E37" s="110"/>
       <c r="F37" s="109" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G37" s="109" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H37" s="122" t="s">
         <v>21</v>
@@ -11116,21 +11076,21 @@
       <c r="A38" s="214"/>
       <c r="B38" s="200"/>
       <c r="C38" s="109" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D38" s="110"/>
       <c r="E38" s="110"/>
       <c r="F38" s="109" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G38" s="109" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H38" s="122" t="s">
         <v>21</v>
       </c>
       <c r="I38" s="112" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J38" s="112"/>
       <c r="K38" s="112"/>
@@ -11143,15 +11103,15 @@
       <c r="A39" s="214"/>
       <c r="B39" s="200"/>
       <c r="C39" s="114" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D39" s="115"/>
       <c r="E39" s="115"/>
       <c r="F39" s="116" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G39" s="116" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H39" s="117" t="s">
         <v>200</v>
@@ -11168,21 +11128,21 @@
       <c r="A40" s="214"/>
       <c r="B40" s="200"/>
       <c r="C40" s="123" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D40" s="124"/>
       <c r="E40" s="124"/>
       <c r="F40" s="125" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G40" s="125" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H40" s="126" t="s">
         <v>200</v>
       </c>
       <c r="I40" s="127" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J40" s="127"/>
       <c r="K40" s="127"/>
@@ -11195,21 +11155,21 @@
       <c r="A41" s="214"/>
       <c r="B41" s="200"/>
       <c r="C41" s="109" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D41" s="110"/>
       <c r="E41" s="110"/>
       <c r="F41" s="109" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G41" s="109" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H41" s="122" t="s">
         <v>200</v>
       </c>
       <c r="I41" s="112" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J41" s="112"/>
       <c r="K41" s="112"/>
@@ -11222,15 +11182,15 @@
       <c r="A42" s="214"/>
       <c r="B42" s="200"/>
       <c r="C42" s="109" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D42" s="110"/>
       <c r="E42" s="110"/>
       <c r="F42" s="109" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G42" s="109" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H42" s="122" t="s">
         <v>21</v>
@@ -11247,21 +11207,21 @@
       <c r="A43" s="214"/>
       <c r="B43" s="200"/>
       <c r="C43" s="109" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D43" s="110"/>
       <c r="E43" s="110"/>
       <c r="F43" s="109" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G43" s="109" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H43" s="122" t="s">
         <v>200</v>
       </c>
       <c r="I43" s="112" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="J43" s="112"/>
       <c r="K43" s="112"/>
@@ -11274,15 +11234,15 @@
       <c r="A44" s="214"/>
       <c r="B44" s="200"/>
       <c r="C44" s="109" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D44" s="110"/>
       <c r="E44" s="110"/>
       <c r="F44" s="109" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G44" s="109" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H44" s="122" t="s">
         <v>200</v>
@@ -11299,15 +11259,15 @@
       <c r="A45" s="214"/>
       <c r="B45" s="200"/>
       <c r="C45" s="109" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D45" s="110"/>
       <c r="E45" s="110"/>
       <c r="F45" s="109" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G45" s="109" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H45" s="122" t="s">
         <v>21</v>
@@ -11324,15 +11284,15 @@
       <c r="A46" s="214"/>
       <c r="B46" s="201"/>
       <c r="C46" s="109" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D46" s="110"/>
       <c r="E46" s="110"/>
       <c r="F46" s="109" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G46" s="109" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H46" s="122" t="s">
         <v>21</v>
@@ -11351,7 +11311,7 @@
         <v>98</v>
       </c>
       <c r="C47" s="113" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D47" s="130"/>
       <c r="E47" s="130">
@@ -11373,10 +11333,10 @@
       <c r="M47" s="23"/>
       <c r="N47" s="23"/>
       <c r="O47" s="132" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P47" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="S47" s="133"/>
     </row>
@@ -11384,7 +11344,7 @@
       <c r="A48" s="214"/>
       <c r="B48" s="193"/>
       <c r="C48" s="113" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D48" s="130"/>
       <c r="E48" s="130"/>
@@ -11404,10 +11364,10 @@
       <c r="M48" s="23"/>
       <c r="N48" s="23"/>
       <c r="O48" s="24" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P48" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="S48" s="133"/>
     </row>
@@ -11415,7 +11375,7 @@
       <c r="A49" s="214"/>
       <c r="B49" s="193"/>
       <c r="C49" s="113" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D49" s="130"/>
       <c r="E49" s="130"/>
@@ -11435,10 +11395,10 @@
       <c r="M49" s="23"/>
       <c r="N49" s="23"/>
       <c r="O49" s="24" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="P49" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="S49" s="133"/>
     </row>
@@ -11446,7 +11406,7 @@
       <c r="A50" s="214"/>
       <c r="B50" s="193"/>
       <c r="C50" s="113" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D50" s="130"/>
       <c r="E50" s="130"/>
@@ -11474,7 +11434,7 @@
         <v>110</v>
       </c>
       <c r="C51" s="113" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D51" s="130"/>
       <c r="E51" s="130"/>
@@ -11494,17 +11454,17 @@
       <c r="M51" s="23"/>
       <c r="N51" s="23"/>
       <c r="O51" s="24" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="P51" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="52" spans="1:19">
       <c r="A52" s="214"/>
       <c r="B52" s="193"/>
       <c r="C52" s="113" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D52" s="130"/>
       <c r="E52" s="130"/>
@@ -11524,17 +11484,17 @@
       <c r="M52" s="23"/>
       <c r="N52" s="23"/>
       <c r="O52" s="24" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P52" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="53" spans="1:19">
       <c r="A53" s="214"/>
       <c r="B53" s="193"/>
       <c r="C53" s="113" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D53" s="130"/>
       <c r="E53" s="130"/>
@@ -11559,7 +11519,7 @@
       <c r="A54" s="214"/>
       <c r="B54" s="193"/>
       <c r="C54" s="113" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D54" s="130"/>
       <c r="E54" s="130"/>
@@ -11584,7 +11544,7 @@
       <c r="A55" s="214"/>
       <c r="B55" s="193"/>
       <c r="C55" s="113" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D55" s="130"/>
       <c r="E55" s="130"/>
@@ -11609,7 +11569,7 @@
       <c r="A56" s="214"/>
       <c r="B56" s="193"/>
       <c r="C56" s="113" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D56" s="130"/>
       <c r="E56" s="130"/>
@@ -11629,17 +11589,17 @@
       <c r="M56" s="23"/>
       <c r="N56" s="23"/>
       <c r="O56" s="24" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P56" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="57" spans="1:19">
       <c r="A57" s="214"/>
       <c r="B57" s="193"/>
       <c r="C57" s="113" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D57" s="130"/>
       <c r="E57" s="130"/>
@@ -11664,7 +11624,7 @@
       <c r="A58" s="214"/>
       <c r="B58" s="193"/>
       <c r="C58" s="113" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D58" s="130"/>
       <c r="E58" s="130"/>
@@ -11684,10 +11644,10 @@
       <c r="M58" s="23"/>
       <c r="N58" s="23"/>
       <c r="O58" s="25" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="P58" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -11767,43 +11727,43 @@
     <row r="1" spans="1:20" ht="19.5">
       <c r="A1" s="134"/>
       <c r="B1" s="135" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C1" s="135" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D1" s="135" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E1" s="135" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F1" s="135" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G1" s="135"/>
       <c r="H1" s="135" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I1" s="135"/>
       <c r="J1" s="135" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="K1" s="136" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L1" s="136" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M1" s="136"/>
       <c r="N1" s="137" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O1" s="138"/>
       <c r="P1" s="138"/>
       <c r="Q1" s="139"/>
       <c r="R1" s="139" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="S1" s="139"/>
       <c r="T1" s="139"/>
@@ -11811,61 +11771,61 @@
     <row r="2" spans="1:20" ht="19.5">
       <c r="A2" s="140"/>
       <c r="B2" s="141" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C2" s="141" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D2" s="142" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E2" s="143" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F2" s="143" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G2" s="143" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H2" s="143" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="I2" s="143" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J2" s="144" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K2" s="145" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L2" s="145" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M2" s="146" t="s">
         <v>150</v>
       </c>
       <c r="N2" s="147" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O2" s="148" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P2" s="148" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q2" s="149" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="R2" s="150" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="S2" s="151" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="T2" s="152" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -11873,26 +11833,26 @@
         <v>13</v>
       </c>
       <c r="B3" s="155" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C3" s="80"/>
       <c r="D3" s="80" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E3" s="80" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F3" s="156"/>
       <c r="G3" s="80" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H3" s="80"/>
       <c r="I3" s="80"/>
       <c r="J3" s="157" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K3" s="80" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L3" s="80"/>
       <c r="M3" s="80"/>
@@ -11911,23 +11871,23 @@
         <v>14</v>
       </c>
       <c r="B4" s="49" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C4" s="182" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F4" s="23"/>
       <c r="G4" s="23"/>
       <c r="H4" s="23"/>
       <c r="I4" s="23"/>
       <c r="J4" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K4" s="23"/>
       <c r="L4" s="23"/>
@@ -11947,21 +11907,21 @@
         <v>15</v>
       </c>
       <c r="B5" s="49" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C5" s="49"/>
       <c r="D5" s="23" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F5" s="23"/>
       <c r="G5" s="23"/>
       <c r="H5" s="23"/>
       <c r="I5" s="23"/>
       <c r="J5" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K5" s="23"/>
       <c r="L5" s="23"/>
@@ -11981,21 +11941,21 @@
         <v>16</v>
       </c>
       <c r="B6" s="49" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C6" s="49"/>
       <c r="D6" s="23" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F6" s="23"/>
       <c r="G6" s="23"/>
       <c r="H6" s="23"/>
       <c r="I6" s="23"/>
       <c r="J6" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K6" s="23"/>
       <c r="L6" s="23"/>
@@ -12015,23 +11975,23 @@
         <v>17</v>
       </c>
       <c r="B7" s="49" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C7" s="182" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F7" s="23"/>
       <c r="G7" s="23"/>
       <c r="H7" s="23"/>
       <c r="I7" s="23"/>
       <c r="J7" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K7" s="23"/>
       <c r="L7" s="23"/>
@@ -12051,21 +12011,21 @@
         <v>18</v>
       </c>
       <c r="B8" s="49" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C8" s="49"/>
       <c r="D8" s="23" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F8" s="23"/>
       <c r="G8" s="23"/>
       <c r="H8" s="23"/>
       <c r="I8" s="23"/>
       <c r="J8" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K8" s="23"/>
       <c r="L8" s="23"/>
@@ -12085,21 +12045,21 @@
         <v>19</v>
       </c>
       <c r="B9" s="49" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C9" s="49"/>
       <c r="D9" s="23" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F9" s="23"/>
       <c r="G9" s="23"/>
       <c r="H9" s="23"/>
       <c r="I9" s="23"/>
       <c r="J9" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K9" s="23"/>
       <c r="L9" s="23"/>
@@ -12119,23 +12079,23 @@
         <v>20</v>
       </c>
       <c r="B10" s="49" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C10" s="183" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F10" s="23"/>
       <c r="G10" s="23"/>
       <c r="H10" s="23"/>
       <c r="I10" s="23"/>
       <c r="J10" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K10" s="23"/>
       <c r="L10" s="23"/>
@@ -12155,23 +12115,23 @@
         <v>21</v>
       </c>
       <c r="B11" s="49" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C11" s="183" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F11" s="23"/>
       <c r="G11" s="23"/>
       <c r="H11" s="23"/>
       <c r="I11" s="23"/>
       <c r="J11" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K11" s="23"/>
       <c r="L11" s="23"/>
@@ -12191,23 +12151,23 @@
         <v>22</v>
       </c>
       <c r="B12" s="49" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C12" s="183" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F12" s="23"/>
       <c r="G12" s="23"/>
       <c r="H12" s="23"/>
       <c r="I12" s="23"/>
       <c r="J12" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K12" s="23"/>
       <c r="L12" s="23"/>
@@ -12227,23 +12187,23 @@
         <v>23</v>
       </c>
       <c r="B13" s="49" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C13" s="183" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F13" s="23"/>
       <c r="G13" s="23"/>
       <c r="H13" s="23"/>
       <c r="I13" s="23"/>
       <c r="J13" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K13" s="23"/>
       <c r="L13" s="23"/>
@@ -12263,23 +12223,23 @@
         <v>24</v>
       </c>
       <c r="B14" s="49" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C14" s="183" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F14" s="23"/>
       <c r="G14" s="23"/>
       <c r="H14" s="23"/>
       <c r="I14" s="23"/>
       <c r="J14" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K14" s="23"/>
       <c r="L14" s="23"/>
@@ -12299,23 +12259,23 @@
         <v>25</v>
       </c>
       <c r="B15" s="49" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C15" s="183" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
       <c r="H15" s="23"/>
       <c r="I15" s="23"/>
       <c r="J15" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K15" s="23"/>
       <c r="L15" s="23"/>
@@ -12335,25 +12295,25 @@
         <v>26</v>
       </c>
       <c r="B16" s="49" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C16" s="183" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F16" s="23" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="G16" s="23"/>
       <c r="H16" s="23"/>
       <c r="I16" s="23"/>
       <c r="J16" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K16" s="23"/>
       <c r="L16" s="23"/>
@@ -12375,23 +12335,23 @@
         <v>27</v>
       </c>
       <c r="B17" s="49" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C17" s="183" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F17" s="23"/>
       <c r="G17" s="23"/>
       <c r="H17" s="23"/>
       <c r="I17" s="23"/>
       <c r="J17" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K17" s="23"/>
       <c r="L17" s="23"/>
@@ -12411,23 +12371,23 @@
         <v>28</v>
       </c>
       <c r="B18" s="49" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C18" s="183" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F18" s="23"/>
       <c r="G18" s="23"/>
       <c r="H18" s="23"/>
       <c r="I18" s="23"/>
       <c r="J18" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K18" s="23"/>
       <c r="L18" s="23"/>
@@ -12449,23 +12409,23 @@
         <v>29</v>
       </c>
       <c r="B19" s="49" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C19" s="183" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F19" s="23"/>
       <c r="G19" s="23"/>
       <c r="H19" s="23"/>
       <c r="I19" s="23"/>
       <c r="J19" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K19" s="23"/>
       <c r="L19" s="23"/>
@@ -12487,23 +12447,23 @@
         <v>30</v>
       </c>
       <c r="B20" s="49" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C20" s="183" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F20" s="23"/>
       <c r="G20" s="23"/>
       <c r="H20" s="23"/>
       <c r="I20" s="23"/>
       <c r="J20" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K20" s="23"/>
       <c r="L20" s="23"/>
@@ -12523,25 +12483,25 @@
         <v>31</v>
       </c>
       <c r="B21" s="49" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C21" s="183" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F21" s="23" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G21" s="23"/>
       <c r="H21" s="23"/>
       <c r="I21" s="23"/>
       <c r="J21" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K21" s="23"/>
       <c r="L21" s="23"/>
@@ -12563,25 +12523,25 @@
         <v>32</v>
       </c>
       <c r="B22" s="49" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C22" s="183" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F22" s="23" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G22" s="23"/>
       <c r="H22" s="23"/>
       <c r="I22" s="23"/>
       <c r="J22" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K22" s="23"/>
       <c r="L22" s="23"/>
@@ -12603,25 +12563,25 @@
         <v>33</v>
       </c>
       <c r="B23" s="49" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C23" s="183" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F23" s="23" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="G23" s="23"/>
       <c r="H23" s="23"/>
       <c r="I23" s="23"/>
       <c r="J23" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K23" s="23"/>
       <c r="L23" s="23"/>
@@ -12643,23 +12603,23 @@
         <v>34</v>
       </c>
       <c r="B24" s="49" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C24" s="183" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F24" s="23"/>
       <c r="G24" s="23"/>
       <c r="H24" s="23"/>
       <c r="I24" s="23"/>
       <c r="J24" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K24" s="23"/>
       <c r="L24" s="23"/>
@@ -12679,23 +12639,23 @@
         <v>35</v>
       </c>
       <c r="B25" s="49" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C25" s="183" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F25" s="23"/>
       <c r="G25" s="23"/>
       <c r="H25" s="23"/>
       <c r="I25" s="23"/>
       <c r="J25" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K25" s="23"/>
       <c r="L25" s="23"/>
@@ -12715,25 +12675,25 @@
         <v>36</v>
       </c>
       <c r="B26" s="49" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C26" s="183" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F26" s="23" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="G26" s="23"/>
       <c r="H26" s="23"/>
       <c r="I26" s="23"/>
       <c r="J26" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K26" s="23"/>
       <c r="L26" s="23"/>
@@ -12755,23 +12715,23 @@
         <v>37</v>
       </c>
       <c r="B27" s="49" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C27" s="183" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F27" s="23"/>
       <c r="G27" s="23"/>
       <c r="H27" s="23"/>
       <c r="I27" s="23"/>
       <c r="J27" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K27" s="23"/>
       <c r="L27" s="23"/>
@@ -12793,23 +12753,23 @@
         <v>38</v>
       </c>
       <c r="B28" s="49" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C28" s="183" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F28" s="23"/>
       <c r="G28" s="23"/>
       <c r="H28" s="23"/>
       <c r="I28" s="23"/>
       <c r="J28" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K28" s="23"/>
       <c r="L28" s="23"/>
@@ -12829,25 +12789,25 @@
         <v>39</v>
       </c>
       <c r="B29" s="49" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C29" s="183" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F29" s="23" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G29" s="23"/>
       <c r="H29" s="23"/>
       <c r="I29" s="23"/>
       <c r="J29" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K29" s="23"/>
       <c r="L29" s="23"/>
@@ -12869,23 +12829,23 @@
         <v>40</v>
       </c>
       <c r="B30" s="49" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C30" s="183" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D30" s="23" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F30" s="23"/>
       <c r="G30" s="23"/>
       <c r="H30" s="23"/>
       <c r="I30" s="23"/>
       <c r="J30" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K30" s="23"/>
       <c r="L30" s="23"/>
@@ -12905,25 +12865,25 @@
         <v>41</v>
       </c>
       <c r="B31" s="49" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C31" s="183" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="D31" s="23" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F31" s="23" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="G31" s="23"/>
       <c r="H31" s="23"/>
       <c r="I31" s="23"/>
       <c r="J31" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K31" s="23"/>
       <c r="L31" s="23"/>
@@ -12945,25 +12905,25 @@
         <v>42</v>
       </c>
       <c r="B32" s="49" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C32" s="183" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="D32" s="23" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F32" s="23" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G32" s="23"/>
       <c r="H32" s="23"/>
       <c r="I32" s="23"/>
       <c r="J32" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K32" s="23"/>
       <c r="L32" s="23"/>
@@ -12985,25 +12945,25 @@
         <v>43</v>
       </c>
       <c r="B33" s="49" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C33" s="183" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="D33" s="23" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F33" s="23" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="G33" s="23"/>
       <c r="H33" s="23"/>
       <c r="I33" s="23"/>
       <c r="J33" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K33" s="23"/>
       <c r="L33" s="23"/>
@@ -13025,23 +12985,23 @@
         <v>44</v>
       </c>
       <c r="B34" s="49" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C34" s="183" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D34" s="23" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E34" s="23" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F34" s="23"/>
       <c r="G34" s="23"/>
       <c r="H34" s="23"/>
       <c r="I34" s="23"/>
       <c r="J34" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K34" s="23"/>
       <c r="L34" s="23"/>
@@ -13061,23 +13021,23 @@
         <v>45</v>
       </c>
       <c r="B35" s="49" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C35" s="183" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="D35" s="23" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E35" s="23" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F35" s="23"/>
       <c r="G35" s="23"/>
       <c r="H35" s="23"/>
       <c r="I35" s="23"/>
       <c r="J35" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K35" s="23"/>
       <c r="L35" s="23"/>
@@ -13097,23 +13057,23 @@
         <v>46</v>
       </c>
       <c r="B36" s="49" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C36" s="183" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D36" s="23" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E36" s="23" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F36" s="23"/>
       <c r="G36" s="23"/>
       <c r="H36" s="23"/>
       <c r="I36" s="23"/>
       <c r="J36" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K36" s="23"/>
       <c r="L36" s="23"/>
@@ -13133,23 +13093,23 @@
         <v>47</v>
       </c>
       <c r="B37" s="49" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C37" s="183" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D37" s="23" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E37" s="23" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F37" s="23"/>
       <c r="G37" s="23"/>
       <c r="H37" s="23"/>
       <c r="I37" s="23"/>
       <c r="J37" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K37" s="23"/>
       <c r="L37" s="23"/>
@@ -13169,23 +13129,23 @@
         <v>48</v>
       </c>
       <c r="B38" s="49" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C38" s="183" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="D38" s="23" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E38" s="23" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F38" s="23"/>
       <c r="G38" s="23"/>
       <c r="H38" s="23"/>
       <c r="I38" s="23"/>
       <c r="J38" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K38" s="23"/>
       <c r="L38" s="23"/>
@@ -13207,25 +13167,25 @@
         <v>49</v>
       </c>
       <c r="B39" s="49" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C39" s="183" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D39" s="23" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E39" s="23" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F39" s="23" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="G39" s="23"/>
       <c r="H39" s="23"/>
       <c r="I39" s="23"/>
       <c r="J39" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K39" s="23"/>
       <c r="L39" s="23"/>
@@ -13247,23 +13207,23 @@
         <v>50</v>
       </c>
       <c r="B40" s="49" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C40" s="183" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D40" s="23" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E40" s="23" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F40" s="23"/>
       <c r="G40" s="23"/>
       <c r="H40" s="23"/>
       <c r="I40" s="23"/>
       <c r="J40" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K40" s="23"/>
       <c r="L40" s="23"/>
@@ -13283,23 +13243,23 @@
         <v>51</v>
       </c>
       <c r="B41" s="49" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C41" s="183" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D41" s="23" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E41" s="23" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F41" s="23"/>
       <c r="G41" s="23"/>
       <c r="H41" s="23"/>
       <c r="I41" s="23"/>
       <c r="J41" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K41" s="23"/>
       <c r="L41" s="23"/>
@@ -13319,23 +13279,23 @@
         <v>52</v>
       </c>
       <c r="B42" s="49" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C42" s="183" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D42" s="23" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E42" s="23" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F42" s="23"/>
       <c r="G42" s="23"/>
       <c r="H42" s="23"/>
       <c r="I42" s="23"/>
       <c r="J42" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K42" s="23"/>
       <c r="L42" s="23"/>
@@ -13355,23 +13315,23 @@
         <v>53</v>
       </c>
       <c r="B43" s="49" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C43" s="183" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D43" s="23" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E43" s="23" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F43" s="23"/>
       <c r="G43" s="23"/>
       <c r="H43" s="23"/>
       <c r="I43" s="23"/>
       <c r="J43" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K43" s="23"/>
       <c r="L43" s="23"/>
@@ -13391,25 +13351,25 @@
         <v>54</v>
       </c>
       <c r="B44" s="49" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C44" s="183" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D44" s="23" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E44" s="23" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F44" s="23" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G44" s="23"/>
       <c r="H44" s="23"/>
       <c r="I44" s="23"/>
       <c r="J44" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K44" s="23"/>
       <c r="L44" s="23"/>
@@ -13431,23 +13391,23 @@
         <v>55</v>
       </c>
       <c r="B45" s="49" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C45" s="183" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="D45" s="23" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E45" s="23" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F45" s="23"/>
       <c r="G45" s="23"/>
       <c r="H45" s="23"/>
       <c r="I45" s="23"/>
       <c r="J45" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K45" s="23"/>
       <c r="L45" s="23"/>
@@ -13467,23 +13427,23 @@
         <v>56</v>
       </c>
       <c r="B46" s="49" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C46" s="183" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D46" s="23" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E46" s="23" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F46" s="23"/>
       <c r="G46" s="23"/>
       <c r="H46" s="23"/>
       <c r="I46" s="23"/>
       <c r="J46" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K46" s="23"/>
       <c r="L46" s="23"/>
@@ -13503,21 +13463,21 @@
         <v>57</v>
       </c>
       <c r="B47" s="49" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C47" s="23"/>
       <c r="D47" s="23" t="s">
         <v>150</v>
       </c>
       <c r="E47" s="23" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F47" s="23"/>
       <c r="G47" s="23"/>
       <c r="H47" s="23"/>
       <c r="I47" s="23"/>
       <c r="J47" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K47" s="23"/>
       <c r="L47" s="23"/>
@@ -13571,43 +13531,43 @@
     <row r="1" spans="1:20" ht="19.5">
       <c r="A1" s="134"/>
       <c r="B1" s="135" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C1" s="135" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D1" s="135" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E1" s="135" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F1" s="135" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G1" s="135"/>
       <c r="H1" s="135" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I1" s="135"/>
       <c r="J1" s="135" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="K1" s="136" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L1" s="136" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M1" s="136"/>
       <c r="N1" s="137" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O1" s="138"/>
       <c r="P1" s="138"/>
       <c r="Q1" s="139"/>
       <c r="R1" s="139" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="S1" s="139"/>
       <c r="T1" s="139"/>
@@ -13615,61 +13575,61 @@
     <row r="2" spans="1:20" ht="19.5">
       <c r="A2" s="140"/>
       <c r="B2" s="141" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C2" s="141" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D2" s="142" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E2" s="143" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F2" s="143" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G2" s="143" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H2" s="143" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="I2" s="143" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J2" s="144" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K2" s="145" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L2" s="145" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M2" s="146" t="s">
         <v>150</v>
       </c>
       <c r="N2" s="147" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O2" s="148" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P2" s="148" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q2" s="149" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="R2" s="150" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="S2" s="151" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="T2" s="152" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -13677,26 +13637,26 @@
         <v>13</v>
       </c>
       <c r="B3" s="155" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C3" s="80"/>
       <c r="D3" s="80" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E3" s="80" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F3" s="156"/>
       <c r="G3" s="80" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H3" s="80"/>
       <c r="I3" s="80"/>
       <c r="J3" s="157" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K3" s="80" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L3" s="80"/>
       <c r="M3" s="80"/>
@@ -13715,23 +13675,23 @@
         <v>14</v>
       </c>
       <c r="B4" s="49" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F4" s="154"/>
       <c r="G4" s="23"/>
       <c r="H4" s="23"/>
       <c r="I4" s="23"/>
       <c r="J4" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K4" s="23"/>
       <c r="L4" s="23"/>
@@ -13751,21 +13711,21 @@
         <v>15</v>
       </c>
       <c r="B5" s="49" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C5" s="23"/>
       <c r="D5" s="23" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F5" s="154"/>
       <c r="G5" s="23"/>
       <c r="H5" s="23"/>
       <c r="I5" s="23"/>
       <c r="J5" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K5" s="23"/>
       <c r="L5" s="23"/>
@@ -13785,21 +13745,21 @@
         <v>16</v>
       </c>
       <c r="B6" s="49" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C6" s="23"/>
       <c r="D6" s="23" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F6" s="154"/>
       <c r="G6" s="23"/>
       <c r="H6" s="23"/>
       <c r="I6" s="23"/>
       <c r="J6" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K6" s="23"/>
       <c r="L6" s="23"/>
@@ -13819,23 +13779,23 @@
         <v>17</v>
       </c>
       <c r="B7" s="49" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F7" s="154"/>
       <c r="G7" s="23"/>
       <c r="H7" s="23"/>
       <c r="I7" s="23"/>
       <c r="J7" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K7" s="23"/>
       <c r="L7" s="23"/>
@@ -13855,21 +13815,21 @@
         <v>18</v>
       </c>
       <c r="B8" s="49" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C8" s="23"/>
       <c r="D8" s="23" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F8" s="154"/>
       <c r="G8" s="23"/>
       <c r="H8" s="23"/>
       <c r="I8" s="23"/>
       <c r="J8" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K8" s="23"/>
       <c r="L8" s="23"/>
@@ -13889,21 +13849,21 @@
         <v>19</v>
       </c>
       <c r="B9" s="49" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C9" s="23"/>
       <c r="D9" s="23" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F9" s="154"/>
       <c r="G9" s="23"/>
       <c r="H9" s="23"/>
       <c r="I9" s="23"/>
       <c r="J9" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K9" s="23"/>
       <c r="L9" s="23"/>
@@ -13923,23 +13883,23 @@
         <v>20</v>
       </c>
       <c r="B10" s="49" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F10" s="154"/>
       <c r="G10" s="23"/>
       <c r="H10" s="23"/>
       <c r="I10" s="23"/>
       <c r="J10" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K10" s="23"/>
       <c r="L10" s="23"/>
@@ -13959,23 +13919,23 @@
         <v>21</v>
       </c>
       <c r="B11" s="49" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F11" s="154"/>
       <c r="G11" s="23"/>
       <c r="H11" s="23"/>
       <c r="I11" s="23"/>
       <c r="J11" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K11" s="23"/>
       <c r="L11" s="23"/>
@@ -13995,23 +13955,23 @@
         <v>22</v>
       </c>
       <c r="B12" s="49" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F12" s="154"/>
       <c r="G12" s="23"/>
       <c r="H12" s="23"/>
       <c r="I12" s="23"/>
       <c r="J12" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K12" s="23"/>
       <c r="L12" s="23"/>
@@ -14031,23 +13991,23 @@
         <v>23</v>
       </c>
       <c r="B13" s="49" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F13" s="154"/>
       <c r="G13" s="23"/>
       <c r="H13" s="23"/>
       <c r="I13" s="23"/>
       <c r="J13" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K13" s="23"/>
       <c r="L13" s="23"/>
@@ -14067,23 +14027,23 @@
         <v>24</v>
       </c>
       <c r="B14" s="49" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F14" s="154"/>
       <c r="G14" s="23"/>
       <c r="H14" s="23"/>
       <c r="I14" s="23"/>
       <c r="J14" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K14" s="23"/>
       <c r="L14" s="23"/>
@@ -14103,23 +14063,23 @@
         <v>25</v>
       </c>
       <c r="B15" s="49" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F15" s="154"/>
       <c r="G15" s="23"/>
       <c r="H15" s="23"/>
       <c r="I15" s="23"/>
       <c r="J15" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K15" s="23"/>
       <c r="L15" s="23"/>
@@ -14139,25 +14099,25 @@
         <v>26</v>
       </c>
       <c r="B16" s="49" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F16" s="154" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="G16" s="23"/>
       <c r="H16" s="23"/>
       <c r="I16" s="23"/>
       <c r="J16" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K16" s="23"/>
       <c r="L16" s="23"/>
@@ -14179,23 +14139,23 @@
         <v>27</v>
       </c>
       <c r="B17" s="49" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="F17" s="154"/>
       <c r="G17" s="23"/>
       <c r="H17" s="23"/>
       <c r="I17" s="23"/>
       <c r="J17" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K17" s="23"/>
       <c r="L17" s="23"/>
@@ -14217,23 +14177,23 @@
         <v>28</v>
       </c>
       <c r="B18" s="49" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="F18" s="154"/>
       <c r="G18" s="23"/>
       <c r="H18" s="23"/>
       <c r="I18" s="23"/>
       <c r="J18" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K18" s="23"/>
       <c r="L18" s="23"/>
@@ -14255,23 +14215,23 @@
         <v>29</v>
       </c>
       <c r="B19" s="49" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="F19" s="154"/>
       <c r="G19" s="23"/>
       <c r="H19" s="23"/>
       <c r="I19" s="23"/>
       <c r="J19" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K19" s="23"/>
       <c r="L19" s="23"/>
@@ -14293,23 +14253,23 @@
         <v>30</v>
       </c>
       <c r="B20" s="49" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F20" s="154"/>
       <c r="G20" s="23"/>
       <c r="H20" s="23"/>
       <c r="I20" s="23"/>
       <c r="J20" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K20" s="23"/>
       <c r="L20" s="23"/>
@@ -14329,25 +14289,25 @@
         <v>31</v>
       </c>
       <c r="B21" s="49" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="F21" s="154" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="G21" s="23"/>
       <c r="H21" s="23"/>
       <c r="I21" s="23"/>
       <c r="J21" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K21" s="23"/>
       <c r="L21" s="23"/>
@@ -14369,25 +14329,25 @@
         <v>32</v>
       </c>
       <c r="B22" s="49" t="s">
+        <v>584</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>813</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>585</v>
+      </c>
+      <c r="E22" s="23" t="s">
+        <v>586</v>
+      </c>
+      <c r="F22" s="154" t="s">
         <v>583</v>
-      </c>
-      <c r="C22" s="23" t="s">
-        <v>812</v>
-      </c>
-      <c r="D22" s="23" t="s">
-        <v>584</v>
-      </c>
-      <c r="E22" s="23" t="s">
-        <v>585</v>
-      </c>
-      <c r="F22" s="154" t="s">
-        <v>582</v>
       </c>
       <c r="G22" s="23"/>
       <c r="H22" s="23"/>
       <c r="I22" s="23"/>
       <c r="J22" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K22" s="23"/>
       <c r="L22" s="23"/>
@@ -14409,25 +14369,25 @@
         <v>33</v>
       </c>
       <c r="B23" s="49" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F23" s="154" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G23" s="23"/>
       <c r="H23" s="23"/>
       <c r="I23" s="23"/>
       <c r="J23" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K23" s="23"/>
       <c r="L23" s="23"/>
@@ -14449,25 +14409,25 @@
         <v>34</v>
       </c>
       <c r="B24" s="49" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="F24" s="154" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G24" s="23"/>
       <c r="H24" s="23"/>
       <c r="I24" s="23"/>
       <c r="J24" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K24" s="23"/>
       <c r="L24" s="23"/>
@@ -14489,23 +14449,23 @@
         <v>35</v>
       </c>
       <c r="B25" s="158" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C25" s="158"/>
       <c r="D25" s="158" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E25" s="158" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="F25" s="159" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="G25" s="158"/>
       <c r="H25" s="158"/>
       <c r="I25" s="158"/>
       <c r="J25" s="160" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K25" s="158"/>
       <c r="L25" s="158"/>
@@ -14525,23 +14485,23 @@
         <v>36</v>
       </c>
       <c r="B26" s="158" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C26" s="158"/>
       <c r="D26" s="158" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E26" s="158" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="F26" s="159" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="G26" s="158"/>
       <c r="H26" s="158"/>
       <c r="I26" s="158"/>
       <c r="J26" s="160" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K26" s="158"/>
       <c r="L26" s="158"/>
@@ -14561,25 +14521,25 @@
         <v>37</v>
       </c>
       <c r="B27" s="49" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="F27" s="154" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="G27" s="23"/>
       <c r="H27" s="23"/>
       <c r="I27" s="23"/>
       <c r="J27" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K27" s="23"/>
       <c r="L27" s="23"/>
@@ -14601,23 +14561,23 @@
         <v>38</v>
       </c>
       <c r="B28" s="49" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="F28" s="154"/>
       <c r="G28" s="23"/>
       <c r="H28" s="23"/>
       <c r="I28" s="23"/>
       <c r="J28" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K28" s="23"/>
       <c r="L28" s="23"/>
@@ -14637,23 +14597,23 @@
         <v>39</v>
       </c>
       <c r="B29" s="49" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F29" s="154"/>
       <c r="G29" s="23"/>
       <c r="H29" s="23"/>
       <c r="I29" s="23"/>
       <c r="J29" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K29" s="23"/>
       <c r="L29" s="23"/>
@@ -14675,23 +14635,23 @@
         <v>40</v>
       </c>
       <c r="B30" s="49" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D30" s="23" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="F30" s="154"/>
       <c r="G30" s="23"/>
       <c r="H30" s="23"/>
       <c r="I30" s="23"/>
       <c r="J30" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K30" s="23"/>
       <c r="L30" s="23"/>
@@ -14713,23 +14673,23 @@
         <v>41</v>
       </c>
       <c r="B31" s="49" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D31" s="23" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="F31" s="154"/>
       <c r="G31" s="23"/>
       <c r="H31" s="23"/>
       <c r="I31" s="23"/>
       <c r="J31" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K31" s="23"/>
       <c r="L31" s="23"/>
@@ -14749,23 +14709,23 @@
         <v>42</v>
       </c>
       <c r="B32" s="49" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D32" s="23" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F32" s="154"/>
       <c r="G32" s="23"/>
       <c r="H32" s="23"/>
       <c r="I32" s="23"/>
       <c r="J32" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K32" s="23"/>
       <c r="L32" s="23"/>
@@ -14785,23 +14745,23 @@
         <v>43</v>
       </c>
       <c r="B33" s="49" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D33" s="23" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F33" s="23"/>
       <c r="G33" s="23"/>
       <c r="H33" s="23"/>
       <c r="I33" s="23"/>
       <c r="J33" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K33" s="23"/>
       <c r="L33" s="23"/>
@@ -14821,23 +14781,23 @@
         <v>44</v>
       </c>
       <c r="B34" s="49" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C34" s="23" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="D34" s="23" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E34" s="23" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F34" s="23"/>
       <c r="G34" s="23"/>
       <c r="H34" s="23"/>
       <c r="I34" s="23"/>
       <c r="J34" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K34" s="23"/>
       <c r="L34" s="23"/>
@@ -14859,25 +14819,25 @@
         <v>45</v>
       </c>
       <c r="B35" s="49" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D35" s="23" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E35" s="23" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F35" s="23" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="G35" s="23"/>
       <c r="H35" s="23"/>
       <c r="I35" s="23"/>
       <c r="J35" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K35" s="23"/>
       <c r="L35" s="23"/>
@@ -14899,23 +14859,23 @@
         <v>46</v>
       </c>
       <c r="B36" s="49" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D36" s="23" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E36" s="23" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F36" s="23"/>
       <c r="G36" s="23"/>
       <c r="H36" s="23"/>
       <c r="I36" s="23"/>
       <c r="J36" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K36" s="23"/>
       <c r="L36" s="23"/>
@@ -14935,23 +14895,23 @@
         <v>47</v>
       </c>
       <c r="B37" s="49" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C37" s="23" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D37" s="23" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E37" s="23" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F37" s="23"/>
       <c r="G37" s="23"/>
       <c r="H37" s="23"/>
       <c r="I37" s="23"/>
       <c r="J37" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K37" s="23"/>
       <c r="L37" s="23"/>
@@ -14971,23 +14931,23 @@
         <v>48</v>
       </c>
       <c r="B38" s="49" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C38" s="23" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D38" s="23" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E38" s="23" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F38" s="23"/>
       <c r="G38" s="23"/>
       <c r="H38" s="23"/>
       <c r="I38" s="23"/>
       <c r="J38" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K38" s="23"/>
       <c r="L38" s="23"/>
@@ -15007,23 +14967,23 @@
         <v>49</v>
       </c>
       <c r="B39" s="49" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C39" s="23" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D39" s="23" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E39" s="23" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F39" s="23"/>
       <c r="G39" s="23"/>
       <c r="H39" s="23"/>
       <c r="I39" s="23"/>
       <c r="J39" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K39" s="23"/>
       <c r="L39" s="23"/>
@@ -15043,25 +15003,25 @@
         <v>50</v>
       </c>
       <c r="B40" s="49" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C40" s="23" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D40" s="23" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E40" s="23" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F40" s="23" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G40" s="23"/>
       <c r="H40" s="23"/>
       <c r="I40" s="23"/>
       <c r="J40" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K40" s="23"/>
       <c r="L40" s="23"/>
@@ -15083,23 +15043,23 @@
         <v>51</v>
       </c>
       <c r="B41" s="49" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C41" s="23" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="D41" s="23" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E41" s="23" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F41" s="23"/>
       <c r="G41" s="23"/>
       <c r="H41" s="23"/>
       <c r="I41" s="23"/>
       <c r="J41" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K41" s="23"/>
       <c r="L41" s="23"/>
@@ -15119,23 +15079,23 @@
         <v>52</v>
       </c>
       <c r="B42" s="49" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C42" s="23" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="D42" s="23" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E42" s="23" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="F42" s="23"/>
       <c r="G42" s="23"/>
       <c r="H42" s="23"/>
       <c r="I42" s="23"/>
       <c r="J42" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K42" s="23"/>
       <c r="L42" s="23"/>
@@ -15155,23 +15115,23 @@
         <v>53</v>
       </c>
       <c r="B43" s="49" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C43" s="23" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D43" s="23" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E43" s="23" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F43" s="23"/>
       <c r="G43" s="23"/>
       <c r="H43" s="23"/>
       <c r="I43" s="23"/>
       <c r="J43" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K43" s="23"/>
       <c r="L43" s="23"/>
@@ -15191,23 +15151,23 @@
         <v>54</v>
       </c>
       <c r="B44" s="49" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C44" s="23" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D44" s="23" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E44" s="23" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="F44" s="23"/>
       <c r="G44" s="23"/>
       <c r="H44" s="23"/>
       <c r="I44" s="23"/>
       <c r="J44" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K44" s="23"/>
       <c r="L44" s="23"/>
@@ -15227,21 +15187,21 @@
         <v>55</v>
       </c>
       <c r="B45" s="49" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C45" s="49"/>
       <c r="D45" s="49" t="s">
         <v>150</v>
       </c>
       <c r="E45" s="49" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F45" s="49"/>
       <c r="G45" s="49"/>
       <c r="H45" s="49"/>
       <c r="I45" s="49"/>
       <c r="J45" s="161" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K45" s="49"/>
       <c r="L45" s="49"/>
@@ -15295,43 +15255,43 @@
     <row r="1" spans="1:20" ht="19.5">
       <c r="A1" s="134"/>
       <c r="B1" s="135" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C1" s="135" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D1" s="135" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E1" s="135" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F1" s="135" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G1" s="135"/>
       <c r="H1" s="135" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I1" s="135"/>
       <c r="J1" s="135" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="K1" s="136" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L1" s="136" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M1" s="136"/>
       <c r="N1" s="137" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O1" s="138"/>
       <c r="P1" s="138"/>
       <c r="Q1" s="139"/>
       <c r="R1" s="139" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="S1" s="139"/>
       <c r="T1" s="139"/>
@@ -15339,61 +15299,61 @@
     <row r="2" spans="1:20" ht="19.5">
       <c r="A2" s="140"/>
       <c r="B2" s="141" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C2" s="141" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D2" s="142" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E2" s="143" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F2" s="143" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G2" s="143" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H2" s="143" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="I2" s="143" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J2" s="144" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K2" s="145" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L2" s="145" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M2" s="146" t="s">
         <v>150</v>
       </c>
       <c r="N2" s="147" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O2" s="148" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P2" s="148" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q2" s="149" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="R2" s="150" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="S2" s="151" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="T2" s="152" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -15401,26 +15361,26 @@
         <v>13</v>
       </c>
       <c r="B3" s="155" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C3" s="80"/>
       <c r="D3" s="80" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E3" s="80" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F3" s="156"/>
       <c r="G3" s="80" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H3" s="80"/>
       <c r="I3" s="80"/>
       <c r="J3" s="157" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K3" s="80" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L3" s="80"/>
       <c r="M3" s="80"/>
@@ -15439,23 +15399,23 @@
         <v>14</v>
       </c>
       <c r="B4" s="49" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C4" s="49" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D4" s="49" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E4" s="49" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F4" s="49"/>
       <c r="G4" s="49"/>
       <c r="H4" s="49"/>
       <c r="I4" s="49"/>
       <c r="J4" s="161" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K4" s="49"/>
       <c r="L4" s="49"/>
@@ -15475,21 +15435,21 @@
         <v>15</v>
       </c>
       <c r="B5" s="49" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C5" s="23"/>
       <c r="D5" s="23" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F5" s="23"/>
       <c r="G5" s="23"/>
       <c r="H5" s="23"/>
       <c r="I5" s="23"/>
       <c r="J5" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K5" s="23"/>
       <c r="L5" s="23"/>
@@ -15509,21 +15469,21 @@
         <v>16</v>
       </c>
       <c r="B6" s="49" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C6" s="23"/>
       <c r="D6" s="23" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F6" s="23"/>
       <c r="G6" s="23"/>
       <c r="H6" s="23"/>
       <c r="I6" s="23"/>
       <c r="J6" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K6" s="23"/>
       <c r="L6" s="23"/>
@@ -15543,23 +15503,23 @@
         <v>17</v>
       </c>
       <c r="B7" s="49" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F7" s="23"/>
       <c r="G7" s="23"/>
       <c r="H7" s="23"/>
       <c r="I7" s="23"/>
       <c r="J7" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K7" s="23"/>
       <c r="L7" s="23"/>
@@ -15579,21 +15539,21 @@
         <v>18</v>
       </c>
       <c r="B8" s="49" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C8" s="23"/>
       <c r="D8" s="23" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F8" s="23"/>
       <c r="G8" s="23"/>
       <c r="H8" s="23"/>
       <c r="I8" s="23"/>
       <c r="J8" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K8" s="23"/>
       <c r="L8" s="23"/>
@@ -15613,21 +15573,21 @@
         <v>19</v>
       </c>
       <c r="B9" s="49" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C9" s="23"/>
       <c r="D9" s="23" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F9" s="23"/>
       <c r="G9" s="23"/>
       <c r="H9" s="23"/>
       <c r="I9" s="23"/>
       <c r="J9" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K9" s="23"/>
       <c r="L9" s="23"/>
@@ -15647,16 +15607,16 @@
         <v>20</v>
       </c>
       <c r="B10" s="49" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F10" s="23"/>
       <c r="G10" s="23">
@@ -15665,7 +15625,7 @@
       <c r="H10" s="23"/>
       <c r="I10" s="23"/>
       <c r="J10" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K10" s="23"/>
       <c r="L10" s="23"/>
@@ -15685,16 +15645,16 @@
         <v>21</v>
       </c>
       <c r="B11" s="49" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F11" s="23"/>
       <c r="G11" s="23">
@@ -15703,7 +15663,7 @@
       <c r="H11" s="23"/>
       <c r="I11" s="23"/>
       <c r="J11" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K11" s="23"/>
       <c r="L11" s="23"/>
@@ -15723,16 +15683,16 @@
         <v>22</v>
       </c>
       <c r="B12" s="49" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F12" s="23"/>
       <c r="G12" s="23">
@@ -15741,7 +15701,7 @@
       <c r="H12" s="23"/>
       <c r="I12" s="23"/>
       <c r="J12" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K12" s="23"/>
       <c r="L12" s="23"/>
@@ -15761,16 +15721,16 @@
         <v>23</v>
       </c>
       <c r="B13" s="49" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F13" s="23"/>
       <c r="G13" s="23">
@@ -15779,7 +15739,7 @@
       <c r="H13" s="23"/>
       <c r="I13" s="23"/>
       <c r="J13" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K13" s="23"/>
       <c r="L13" s="23"/>
@@ -15799,16 +15759,16 @@
         <v>24</v>
       </c>
       <c r="B14" s="49" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F14" s="23"/>
       <c r="G14" s="23">
@@ -15817,7 +15777,7 @@
       <c r="H14" s="23"/>
       <c r="I14" s="23"/>
       <c r="J14" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K14" s="23"/>
       <c r="L14" s="23"/>
@@ -15837,16 +15797,16 @@
         <v>25</v>
       </c>
       <c r="B15" s="49" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F15" s="23"/>
       <c r="G15" s="23">
@@ -15855,7 +15815,7 @@
       <c r="H15" s="23"/>
       <c r="I15" s="23"/>
       <c r="J15" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K15" s="23"/>
       <c r="L15" s="23"/>
@@ -15875,25 +15835,25 @@
         <v>26</v>
       </c>
       <c r="B16" s="49" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F16" s="23" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="G16" s="23"/>
       <c r="H16" s="23"/>
       <c r="I16" s="23"/>
       <c r="J16" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K16" s="23"/>
       <c r="L16" s="23"/>
@@ -15915,16 +15875,16 @@
         <v>27</v>
       </c>
       <c r="B17" s="49" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="F17" s="23"/>
       <c r="G17" s="23">
@@ -15933,7 +15893,7 @@
       <c r="H17" s="23"/>
       <c r="I17" s="23"/>
       <c r="J17" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K17" s="23"/>
       <c r="L17" s="23"/>
@@ -15955,16 +15915,16 @@
         <v>28</v>
       </c>
       <c r="B18" s="49" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="F18" s="23"/>
       <c r="G18" s="23">
@@ -15973,7 +15933,7 @@
       <c r="H18" s="23"/>
       <c r="I18" s="23"/>
       <c r="J18" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K18" s="23"/>
       <c r="L18" s="23"/>
@@ -15995,16 +15955,16 @@
         <v>29</v>
       </c>
       <c r="B19" s="49" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="F19" s="23"/>
       <c r="G19" s="23">
@@ -16013,7 +15973,7 @@
       <c r="H19" s="23"/>
       <c r="I19" s="23"/>
       <c r="J19" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K19" s="23"/>
       <c r="L19" s="23"/>
@@ -16035,23 +15995,23 @@
         <v>30</v>
       </c>
       <c r="B20" s="49" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="F20" s="23"/>
       <c r="G20" s="23"/>
       <c r="H20" s="23"/>
       <c r="I20" s="23"/>
       <c r="J20" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K20" s="23"/>
       <c r="L20" s="23"/>
@@ -16071,16 +16031,16 @@
         <v>31</v>
       </c>
       <c r="B21" s="49" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="F21" s="23"/>
       <c r="G21" s="23">
@@ -16089,7 +16049,7 @@
       <c r="H21" s="23"/>
       <c r="I21" s="23"/>
       <c r="J21" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K21" s="23"/>
       <c r="L21" s="23"/>
@@ -16111,16 +16071,16 @@
         <v>32</v>
       </c>
       <c r="B22" s="49" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="F22" s="23"/>
       <c r="G22" s="23">
@@ -16129,7 +16089,7 @@
       <c r="H22" s="23"/>
       <c r="I22" s="23"/>
       <c r="J22" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K22" s="23"/>
       <c r="L22" s="23"/>
@@ -16151,19 +16111,19 @@
         <v>33</v>
       </c>
       <c r="B23" s="49" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F23" s="23" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G23" s="23">
         <v>4008</v>
@@ -16171,7 +16131,7 @@
       <c r="H23" s="23"/>
       <c r="I23" s="23"/>
       <c r="J23" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K23" s="23"/>
       <c r="L23" s="23"/>
@@ -16193,19 +16153,19 @@
         <v>34</v>
       </c>
       <c r="B24" s="49" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="F24" s="23" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G24" s="23">
         <v>2672</v>
@@ -16213,7 +16173,7 @@
       <c r="H24" s="23"/>
       <c r="I24" s="23"/>
       <c r="J24" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K24" s="23"/>
       <c r="L24" s="23"/>
@@ -16235,23 +16195,23 @@
         <v>35</v>
       </c>
       <c r="B25" s="158" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C25" s="158"/>
       <c r="D25" s="158" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E25" s="158" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="F25" s="159" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="G25" s="158"/>
       <c r="H25" s="158"/>
       <c r="I25" s="158"/>
       <c r="J25" s="160" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K25" s="158"/>
       <c r="L25" s="158"/>
@@ -16271,23 +16231,23 @@
         <v>36</v>
       </c>
       <c r="B26" s="158" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C26" s="158"/>
       <c r="D26" s="158" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E26" s="158" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="F26" s="159" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="G26" s="158"/>
       <c r="H26" s="158"/>
       <c r="I26" s="158"/>
       <c r="J26" s="160" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K26" s="158"/>
       <c r="L26" s="158"/>
@@ -16307,19 +16267,19 @@
         <v>37</v>
       </c>
       <c r="B27" s="49" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="F27" s="23" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="G27" s="23">
         <v>4</v>
@@ -16327,7 +16287,7 @@
       <c r="H27" s="23"/>
       <c r="I27" s="23"/>
       <c r="J27" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K27" s="23"/>
       <c r="L27" s="23"/>
@@ -16349,25 +16309,25 @@
         <v>38</v>
       </c>
       <c r="B28" s="49" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="F28" s="23"/>
       <c r="G28" s="23" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H28" s="23"/>
       <c r="I28" s="23"/>
       <c r="J28" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K28" s="23"/>
       <c r="L28" s="23"/>
@@ -16387,16 +16347,16 @@
         <v>39</v>
       </c>
       <c r="B29" s="49" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F29" s="23"/>
       <c r="G29" s="23">
@@ -16405,7 +16365,7 @@
       <c r="H29" s="23"/>
       <c r="I29" s="23"/>
       <c r="J29" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K29" s="23"/>
       <c r="L29" s="23"/>
@@ -16427,23 +16387,23 @@
         <v>40</v>
       </c>
       <c r="B30" s="49" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D30" s="23" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="F30" s="23"/>
       <c r="G30" s="23"/>
       <c r="H30" s="23"/>
       <c r="I30" s="23"/>
       <c r="J30" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K30" s="23"/>
       <c r="L30" s="23"/>
@@ -16465,23 +16425,23 @@
         <v>41</v>
       </c>
       <c r="B31" s="49" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D31" s="23" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="F31" s="23"/>
       <c r="G31" s="23"/>
       <c r="H31" s="23"/>
       <c r="I31" s="23"/>
       <c r="J31" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K31" s="23"/>
       <c r="L31" s="23"/>
@@ -16501,25 +16461,25 @@
         <v>42</v>
       </c>
       <c r="B32" s="49" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D32" s="23" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F32" s="23"/>
       <c r="G32" s="23" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H32" s="23"/>
       <c r="I32" s="23"/>
       <c r="J32" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K32" s="23"/>
       <c r="L32" s="23"/>
@@ -16539,25 +16499,25 @@
         <v>43</v>
       </c>
       <c r="B33" s="49" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D33" s="23" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F33" s="23"/>
       <c r="G33" s="23" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H33" s="23"/>
       <c r="I33" s="23"/>
       <c r="J33" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K33" s="23"/>
       <c r="L33" s="23"/>
@@ -16577,16 +16537,16 @@
         <v>44</v>
       </c>
       <c r="B34" s="49" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C34" s="23" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="D34" s="23" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E34" s="23" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F34" s="23"/>
       <c r="G34" s="23">
@@ -16595,7 +16555,7 @@
       <c r="H34" s="23"/>
       <c r="I34" s="23"/>
       <c r="J34" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K34" s="23"/>
       <c r="L34" s="23"/>
@@ -16617,19 +16577,19 @@
         <v>45</v>
       </c>
       <c r="B35" s="49" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D35" s="23" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E35" s="23" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F35" s="23" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="G35" s="23">
         <v>200000</v>
@@ -16637,7 +16597,7 @@
       <c r="H35" s="23"/>
       <c r="I35" s="23"/>
       <c r="J35" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K35" s="23"/>
       <c r="L35" s="23"/>
@@ -16659,25 +16619,25 @@
         <v>46</v>
       </c>
       <c r="B36" s="49" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D36" s="23" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E36" s="23" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F36" s="23"/>
       <c r="G36" s="23" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H36" s="23"/>
       <c r="I36" s="23"/>
       <c r="J36" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K36" s="23"/>
       <c r="L36" s="23"/>
@@ -16697,25 +16657,25 @@
         <v>47</v>
       </c>
       <c r="B37" s="49" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C37" s="23" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D37" s="23" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E37" s="23" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F37" s="23"/>
       <c r="G37" s="23" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H37" s="23"/>
       <c r="I37" s="23"/>
       <c r="J37" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K37" s="23"/>
       <c r="L37" s="23"/>
@@ -16735,25 +16695,25 @@
         <v>48</v>
       </c>
       <c r="B38" s="49" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C38" s="23" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D38" s="23" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E38" s="23" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F38" s="23"/>
       <c r="G38" s="23" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H38" s="23"/>
       <c r="I38" s="23"/>
       <c r="J38" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K38" s="23"/>
       <c r="L38" s="23"/>
@@ -16773,25 +16733,25 @@
         <v>49</v>
       </c>
       <c r="B39" s="49" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C39" s="23" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D39" s="23" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E39" s="23" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F39" s="23"/>
       <c r="G39" s="23" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H39" s="23"/>
       <c r="I39" s="23"/>
       <c r="J39" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K39" s="23"/>
       <c r="L39" s="23"/>
@@ -16811,19 +16771,19 @@
         <v>50</v>
       </c>
       <c r="B40" s="49" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C40" s="23" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D40" s="23" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E40" s="23" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F40" s="23" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G40" s="23">
         <v>40</v>
@@ -16831,7 +16791,7 @@
       <c r="H40" s="23"/>
       <c r="I40" s="23"/>
       <c r="J40" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K40" s="23"/>
       <c r="L40" s="23"/>
@@ -16853,25 +16813,25 @@
         <v>51</v>
       </c>
       <c r="B41" s="49" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C41" s="23" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="D41" s="23" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E41" s="23" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F41" s="23"/>
       <c r="G41" s="23" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H41" s="23"/>
       <c r="I41" s="23"/>
       <c r="J41" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K41" s="23"/>
       <c r="L41" s="23"/>
@@ -16891,23 +16851,23 @@
         <v>52</v>
       </c>
       <c r="B42" s="49" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C42" s="23" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="D42" s="23" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E42" s="23" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="F42" s="23"/>
       <c r="G42" s="23"/>
       <c r="H42" s="23"/>
       <c r="I42" s="23"/>
       <c r="J42" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K42" s="23"/>
       <c r="L42" s="23"/>
@@ -16927,23 +16887,23 @@
         <v>53</v>
       </c>
       <c r="B43" s="49" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C43" s="23" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D43" s="23" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E43" s="23" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F43" s="23"/>
       <c r="G43" s="23"/>
       <c r="H43" s="23"/>
       <c r="I43" s="23"/>
       <c r="J43" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K43" s="23"/>
       <c r="L43" s="23"/>
@@ -16963,25 +16923,25 @@
         <v>54</v>
       </c>
       <c r="B44" s="49" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C44" s="23" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D44" s="23" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E44" s="23" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="F44" s="23"/>
       <c r="G44" s="23" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H44" s="23"/>
       <c r="I44" s="23"/>
       <c r="J44" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K44" s="23"/>
       <c r="L44" s="23"/>
@@ -17001,21 +16961,21 @@
         <v>55</v>
       </c>
       <c r="B45" s="49" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C45" s="23"/>
       <c r="D45" s="23" t="s">
         <v>150</v>
       </c>
       <c r="E45" s="23" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F45" s="23"/>
       <c r="G45" s="23"/>
       <c r="H45" s="23"/>
       <c r="I45" s="23"/>
       <c r="J45" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K45" s="23"/>
       <c r="L45" s="23"/>
@@ -17069,43 +17029,43 @@
     <row r="1" spans="1:20" ht="19.5">
       <c r="A1" s="134"/>
       <c r="B1" s="135" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C1" s="135" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D1" s="135" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E1" s="135" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F1" s="135" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G1" s="135"/>
       <c r="H1" s="135" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I1" s="135"/>
       <c r="J1" s="135" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="K1" s="136" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L1" s="136" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M1" s="136"/>
       <c r="N1" s="137" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O1" s="138"/>
       <c r="P1" s="138"/>
       <c r="Q1" s="139"/>
       <c r="R1" s="139" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="S1" s="139"/>
       <c r="T1" s="139"/>
@@ -17113,61 +17073,61 @@
     <row r="2" spans="1:20" ht="19.5">
       <c r="A2" s="140"/>
       <c r="B2" s="141" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C2" s="141" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D2" s="142" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E2" s="143" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F2" s="143" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G2" s="143" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H2" s="143" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="I2" s="143" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J2" s="144" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K2" s="145" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L2" s="145" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M2" s="146" t="s">
         <v>150</v>
       </c>
       <c r="N2" s="147" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O2" s="148" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P2" s="148" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q2" s="149" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="R2" s="150" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="S2" s="151" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="T2" s="152" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -17175,26 +17135,26 @@
         <v>13</v>
       </c>
       <c r="B3" s="155" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C3" s="80"/>
       <c r="D3" s="80" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E3" s="80" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F3" s="156"/>
       <c r="G3" s="80" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H3" s="80"/>
       <c r="I3" s="80"/>
       <c r="J3" s="157" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K3" s="80" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L3" s="80"/>
       <c r="M3" s="80"/>
@@ -17213,23 +17173,23 @@
         <v>14</v>
       </c>
       <c r="B4" s="49" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F4" s="23"/>
       <c r="G4" s="23"/>
       <c r="H4" s="23"/>
       <c r="I4" s="23"/>
       <c r="J4" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K4" s="23"/>
       <c r="L4" s="23"/>
@@ -17249,21 +17209,21 @@
         <v>15</v>
       </c>
       <c r="B5" s="49" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C5" s="23"/>
       <c r="D5" s="23" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F5" s="23"/>
       <c r="G5" s="23"/>
       <c r="H5" s="23"/>
       <c r="I5" s="23"/>
       <c r="J5" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K5" s="23"/>
       <c r="L5" s="23"/>
@@ -17283,21 +17243,21 @@
         <v>16</v>
       </c>
       <c r="B6" s="49" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C6" s="23"/>
       <c r="D6" s="23" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F6" s="23"/>
       <c r="G6" s="23"/>
       <c r="H6" s="23"/>
       <c r="I6" s="23"/>
       <c r="J6" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K6" s="23"/>
       <c r="L6" s="23"/>
@@ -17317,23 +17277,23 @@
         <v>17</v>
       </c>
       <c r="B7" s="49" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F7" s="23"/>
       <c r="G7" s="23"/>
       <c r="H7" s="23"/>
       <c r="I7" s="23"/>
       <c r="J7" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K7" s="23"/>
       <c r="L7" s="23"/>
@@ -17353,21 +17313,21 @@
         <v>18</v>
       </c>
       <c r="B8" s="49" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C8" s="23"/>
       <c r="D8" s="23" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F8" s="23"/>
       <c r="G8" s="23"/>
       <c r="H8" s="23"/>
       <c r="I8" s="23"/>
       <c r="J8" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K8" s="23"/>
       <c r="L8" s="23"/>
@@ -17387,21 +17347,21 @@
         <v>19</v>
       </c>
       <c r="B9" s="49" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C9" s="23"/>
       <c r="D9" s="23" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F9" s="23"/>
       <c r="G9" s="23"/>
       <c r="H9" s="23"/>
       <c r="I9" s="23"/>
       <c r="J9" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K9" s="23"/>
       <c r="L9" s="23"/>
@@ -17421,23 +17381,23 @@
         <v>20</v>
       </c>
       <c r="B10" s="49" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F10" s="23"/>
       <c r="G10" s="23"/>
       <c r="H10" s="23"/>
       <c r="I10" s="23"/>
       <c r="J10" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K10" s="23"/>
       <c r="L10" s="23"/>
@@ -17457,23 +17417,23 @@
         <v>21</v>
       </c>
       <c r="B11" s="49" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F11" s="23"/>
       <c r="G11" s="23"/>
       <c r="H11" s="23"/>
       <c r="I11" s="23"/>
       <c r="J11" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K11" s="23"/>
       <c r="L11" s="23"/>
@@ -17493,23 +17453,23 @@
         <v>22</v>
       </c>
       <c r="B12" s="49" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F12" s="23"/>
       <c r="G12" s="23"/>
       <c r="H12" s="23"/>
       <c r="I12" s="23"/>
       <c r="J12" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K12" s="23"/>
       <c r="L12" s="23"/>
@@ -17529,23 +17489,23 @@
         <v>23</v>
       </c>
       <c r="B13" s="49" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F13" s="23"/>
       <c r="G13" s="23"/>
       <c r="H13" s="23"/>
       <c r="I13" s="23"/>
       <c r="J13" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K13" s="23"/>
       <c r="L13" s="23"/>
@@ -17565,23 +17525,23 @@
         <v>24</v>
       </c>
       <c r="B14" s="49" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F14" s="23"/>
       <c r="G14" s="23"/>
       <c r="H14" s="23"/>
       <c r="I14" s="23"/>
       <c r="J14" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K14" s="23"/>
       <c r="L14" s="23"/>
@@ -17601,23 +17561,23 @@
         <v>25</v>
       </c>
       <c r="B15" s="49" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
       <c r="H15" s="23"/>
       <c r="I15" s="23"/>
       <c r="J15" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K15" s="23"/>
       <c r="L15" s="23"/>
@@ -17637,23 +17597,23 @@
         <v>26</v>
       </c>
       <c r="B16" s="49" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="F16" s="23"/>
       <c r="G16" s="23"/>
       <c r="H16" s="23"/>
       <c r="I16" s="23"/>
       <c r="J16" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K16" s="23"/>
       <c r="L16" s="23"/>
@@ -17675,23 +17635,23 @@
         <v>27</v>
       </c>
       <c r="B17" s="49" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="F17" s="23"/>
       <c r="G17" s="23"/>
       <c r="H17" s="23"/>
       <c r="I17" s="23"/>
       <c r="J17" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K17" s="23"/>
       <c r="L17" s="23"/>
@@ -17713,23 +17673,23 @@
         <v>28</v>
       </c>
       <c r="B18" s="49" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="F18" s="23"/>
       <c r="G18" s="23"/>
       <c r="H18" s="23"/>
       <c r="I18" s="23"/>
       <c r="J18" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K18" s="23"/>
       <c r="L18" s="23"/>
@@ -17751,23 +17711,23 @@
         <v>29</v>
       </c>
       <c r="B19" s="49" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="F19" s="23"/>
       <c r="G19" s="23"/>
       <c r="H19" s="23"/>
       <c r="I19" s="23"/>
       <c r="J19" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K19" s="23"/>
       <c r="L19" s="23"/>
@@ -17787,23 +17747,23 @@
         <v>30</v>
       </c>
       <c r="B20" s="49" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="F20" s="23"/>
       <c r="G20" s="23"/>
       <c r="H20" s="23"/>
       <c r="I20" s="23"/>
       <c r="J20" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K20" s="23"/>
       <c r="L20" s="23"/>
@@ -17825,23 +17785,23 @@
         <v>31</v>
       </c>
       <c r="B21" s="49" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="F21" s="23"/>
       <c r="G21" s="23"/>
       <c r="H21" s="23"/>
       <c r="I21" s="23"/>
       <c r="J21" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K21" s="23"/>
       <c r="L21" s="23"/>
@@ -17863,23 +17823,23 @@
         <v>32</v>
       </c>
       <c r="B22" s="49" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="F22" s="23"/>
       <c r="G22" s="23"/>
       <c r="H22" s="23"/>
       <c r="I22" s="23"/>
       <c r="J22" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K22" s="23"/>
       <c r="L22" s="23"/>
@@ -17901,23 +17861,23 @@
         <v>33</v>
       </c>
       <c r="B23" s="49" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="F23" s="23"/>
       <c r="G23" s="23"/>
       <c r="H23" s="23"/>
       <c r="I23" s="23"/>
       <c r="J23" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K23" s="23"/>
       <c r="L23" s="23"/>
@@ -17939,25 +17899,25 @@
         <v>34</v>
       </c>
       <c r="B24" s="49" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F24" s="23" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G24" s="23"/>
       <c r="H24" s="23"/>
       <c r="I24" s="23"/>
       <c r="J24" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K24" s="23"/>
       <c r="L24" s="23"/>
@@ -17979,25 +17939,25 @@
         <v>35</v>
       </c>
       <c r="B25" s="49" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="F25" s="23" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G25" s="23"/>
       <c r="H25" s="23"/>
       <c r="I25" s="23"/>
       <c r="J25" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K25" s="23"/>
       <c r="L25" s="23"/>
@@ -18019,23 +17979,23 @@
         <v>36</v>
       </c>
       <c r="B26" s="158" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C26" s="158"/>
       <c r="D26" s="158" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E26" s="158" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="F26" s="159" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="G26" s="158"/>
       <c r="H26" s="158"/>
       <c r="I26" s="158"/>
       <c r="J26" s="160" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K26" s="158"/>
       <c r="L26" s="158"/>
@@ -18055,23 +18015,23 @@
         <v>37</v>
       </c>
       <c r="B27" s="158" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C27" s="158"/>
       <c r="D27" s="158" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E27" s="158" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="F27" s="159" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="G27" s="158"/>
       <c r="H27" s="158"/>
       <c r="I27" s="158"/>
       <c r="J27" s="160" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K27" s="158"/>
       <c r="L27" s="158"/>
@@ -18091,25 +18051,25 @@
         <v>38</v>
       </c>
       <c r="B28" s="49" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="F28" s="23" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="G28" s="23"/>
       <c r="H28" s="23"/>
       <c r="I28" s="23"/>
       <c r="J28" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K28" s="23"/>
       <c r="L28" s="23"/>
@@ -18131,23 +18091,23 @@
         <v>39</v>
       </c>
       <c r="B29" s="49" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F29" s="23"/>
       <c r="G29" s="23"/>
       <c r="H29" s="23"/>
       <c r="I29" s="23"/>
       <c r="J29" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K29" s="23"/>
       <c r="L29" s="23"/>
@@ -18167,23 +18127,23 @@
         <v>40</v>
       </c>
       <c r="B30" s="49" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D30" s="23" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="F30" s="23"/>
       <c r="G30" s="23"/>
       <c r="H30" s="23"/>
       <c r="I30" s="23"/>
       <c r="J30" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K30" s="23"/>
       <c r="L30" s="23"/>
@@ -18205,25 +18165,25 @@
         <v>41</v>
       </c>
       <c r="B31" s="49" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="D31" s="23" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="F31" s="23" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="G31" s="23"/>
       <c r="H31" s="23"/>
       <c r="I31" s="23"/>
       <c r="J31" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K31" s="23"/>
       <c r="L31" s="23"/>
@@ -18245,23 +18205,23 @@
         <v>42</v>
       </c>
       <c r="B32" s="49" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D32" s="23" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F32" s="23"/>
       <c r="G32" s="23"/>
       <c r="H32" s="23"/>
       <c r="I32" s="23"/>
       <c r="J32" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K32" s="23"/>
       <c r="L32" s="23"/>
@@ -18281,23 +18241,23 @@
         <v>43</v>
       </c>
       <c r="B33" s="49" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D33" s="23" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F33" s="23"/>
       <c r="G33" s="23"/>
       <c r="H33" s="23"/>
       <c r="I33" s="23"/>
       <c r="J33" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K33" s="23"/>
       <c r="L33" s="23"/>
@@ -18317,25 +18277,25 @@
         <v>44</v>
       </c>
       <c r="B34" s="49" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C34" s="23" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="D34" s="23" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="E34" s="23" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="F34" s="23" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G34" s="23"/>
       <c r="H34" s="23"/>
       <c r="I34" s="23"/>
       <c r="J34" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K34" s="23"/>
       <c r="L34" s="23"/>
@@ -18357,25 +18317,25 @@
         <v>45</v>
       </c>
       <c r="B35" s="49" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D35" s="23" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E35" s="23" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F35" s="23" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="G35" s="23"/>
       <c r="H35" s="23"/>
       <c r="I35" s="23"/>
       <c r="J35" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K35" s="23"/>
       <c r="L35" s="23"/>
@@ -18397,23 +18357,23 @@
         <v>46</v>
       </c>
       <c r="B36" s="49" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D36" s="23" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E36" s="23" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F36" s="23"/>
       <c r="G36" s="23"/>
       <c r="H36" s="23"/>
       <c r="I36" s="23"/>
       <c r="J36" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K36" s="23"/>
       <c r="L36" s="23"/>
@@ -18433,23 +18393,23 @@
         <v>47</v>
       </c>
       <c r="B37" s="49" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C37" s="23" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D37" s="23" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E37" s="23" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F37" s="23"/>
       <c r="G37" s="23"/>
       <c r="H37" s="23"/>
       <c r="I37" s="23"/>
       <c r="J37" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K37" s="23"/>
       <c r="L37" s="23"/>
@@ -18469,23 +18429,23 @@
         <v>48</v>
       </c>
       <c r="B38" s="49" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C38" s="23" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D38" s="23" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E38" s="23" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F38" s="23"/>
       <c r="G38" s="23"/>
       <c r="H38" s="23"/>
       <c r="I38" s="23"/>
       <c r="J38" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K38" s="23"/>
       <c r="L38" s="23"/>
@@ -18505,23 +18465,23 @@
         <v>49</v>
       </c>
       <c r="B39" s="49" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C39" s="23" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D39" s="23" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E39" s="23" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F39" s="23"/>
       <c r="G39" s="23"/>
       <c r="H39" s="23"/>
       <c r="I39" s="23"/>
       <c r="J39" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K39" s="23"/>
       <c r="L39" s="23"/>
@@ -18541,23 +18501,23 @@
         <v>50</v>
       </c>
       <c r="B40" s="49" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C40" s="23" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="D40" s="23" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E40" s="23" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F40" s="23"/>
       <c r="G40" s="23"/>
       <c r="H40" s="23"/>
       <c r="I40" s="23"/>
       <c r="J40" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K40" s="23"/>
       <c r="L40" s="23"/>
@@ -18577,23 +18537,23 @@
         <v>51</v>
       </c>
       <c r="B41" s="49" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C41" s="23" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="D41" s="23" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E41" s="23" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="F41" s="23"/>
       <c r="G41" s="23"/>
       <c r="H41" s="23"/>
       <c r="I41" s="23"/>
       <c r="J41" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K41" s="23"/>
       <c r="L41" s="23"/>
@@ -18613,23 +18573,23 @@
         <v>52</v>
       </c>
       <c r="B42" s="49" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C42" s="23" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D42" s="23" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E42" s="23" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F42" s="23"/>
       <c r="G42" s="23"/>
       <c r="H42" s="23"/>
       <c r="I42" s="23"/>
       <c r="J42" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K42" s="23"/>
       <c r="L42" s="23"/>
@@ -18649,23 +18609,23 @@
         <v>53</v>
       </c>
       <c r="B43" s="49" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C43" s="23" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D43" s="23" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="E43" s="23" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="F43" s="23"/>
       <c r="G43" s="23"/>
       <c r="H43" s="23"/>
       <c r="I43" s="23"/>
       <c r="J43" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K43" s="23"/>
       <c r="L43" s="23"/>
@@ -18685,21 +18645,21 @@
         <v>54</v>
       </c>
       <c r="B44" s="49" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C44" s="23"/>
       <c r="D44" s="23" t="s">
         <v>150</v>
       </c>
       <c r="E44" s="23" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F44" s="23"/>
       <c r="G44" s="23"/>
       <c r="H44" s="23"/>
       <c r="I44" s="23"/>
       <c r="J44" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K44" s="23"/>
       <c r="L44" s="23"/>
@@ -18751,7 +18711,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="166" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B2" s="166" t="s">
         <v>18</v>
@@ -18760,18 +18720,18 @@
       <c r="D2" s="223"/>
       <c r="E2" s="224"/>
       <c r="F2" s="167" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="36" customHeight="1">
       <c r="A3" s="166" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B3" s="166" t="s">
         <v>18</v>
       </c>
       <c r="C3" s="225" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D3" s="226"/>
       <c r="E3" s="227"/>
@@ -18779,13 +18739,13 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="166" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B4" s="166" t="s">
         <v>18</v>
       </c>
       <c r="C4" s="228" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D4" s="229"/>
       <c r="E4" s="230"/>
@@ -18793,30 +18753,30 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="169" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B5" s="169"/>
       <c r="C5" s="170" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="D5" s="170" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E5" s="170" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="F5" s="168"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="217" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B6" s="169"/>
       <c r="C6" s="96" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D6" s="171" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="E6" s="172"/>
       <c r="F6" s="167"/>
@@ -18825,13 +18785,13 @@
       <c r="A7" s="218"/>
       <c r="B7" s="169"/>
       <c r="C7" s="215" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="D7" s="171" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="E7" s="172" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="F7" s="167"/>
     </row>
@@ -18840,10 +18800,10 @@
       <c r="B8" s="176"/>
       <c r="C8" s="216"/>
       <c r="D8" s="174" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="E8" s="175" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="F8" s="167" t="e" vm="1">
         <v>#VALUE!</v>
@@ -18852,16 +18812,16 @@
     <row r="9" spans="1:6" ht="177" customHeight="1">
       <c r="A9" s="218"/>
       <c r="B9" s="173" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C9" s="177" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="D9" s="174" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="E9" s="177" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="F9" s="178" t="e" vm="2">
         <v>#VALUE!</v>
@@ -18871,13 +18831,13 @@
       <c r="A10" s="218"/>
       <c r="B10" s="169"/>
       <c r="C10" s="177" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="D10" s="174" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="E10" s="177" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="F10" s="178" t="e" vm="2">
         <v>#VALUE!</v>
@@ -18898,17 +18858,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7e1b7570-88a0-44ee-ab1c-d900d3a9ef2f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="69806635-1477-418f-8922-2a2d0bbc39e0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101000ED353C60105F34DABBBF603193D9FD7" ma:contentTypeVersion="8" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="ff96f1b83903b6ca69e21ae72ce65d29">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7e1b7570-88a0-44ee-ab1c-d900d3a9ef2f" xmlns:ns3="69806635-1477-418f-8922-2a2d0bbc39e0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dd34249053b4960b9f5dac26d98b1ad9" ns2:_="" ns3:_="">
     <xsd:import namespace="7e1b7570-88a0-44ee-ab1c-d900d3a9ef2f"/>
@@ -19085,7 +19034,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -19094,18 +19043,18 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB043C42-5D59-4A30-92A0-5EA74B604AF5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="7e1b7570-88a0-44ee-ab1c-d900d3a9ef2f"/>
-    <ds:schemaRef ds:uri="69806635-1477-418f-8922-2a2d0bbc39e0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7e1b7570-88a0-44ee-ab1c-d900d3a9ef2f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="69806635-1477-418f-8922-2a2d0bbc39e0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C04DD24-2E45-4DC0-B69F-E7DC5E36A116}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19124,10 +19073,21 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F1080EF-91B6-417D-A249-69224D257C51}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB043C42-5D59-4A30-92A0-5EA74B604AF5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="7e1b7570-88a0-44ee-ab1c-d900d3a9ef2f"/>
+    <ds:schemaRef ds:uri="69806635-1477-418f-8922-2a2d0bbc39e0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>